--- a/artfynd/A 55216-2022 artfynd.xlsx
+++ b/artfynd/A 55216-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119803564</v>
       </c>
       <c r="B2" t="n">
-        <v>57679</v>
+        <v>57689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55216-2022 artfynd.xlsx
+++ b/artfynd/A 55216-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>119803564</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,6 +781,516 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>97567813</v>
+      </c>
+      <c r="B3" t="n">
+        <v>43378</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>201075</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Boloria selene</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ramsjö, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>535516</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6904761</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-07-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-07-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Inventering för länsstyrelsen</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind, Tor Hansson Frank, Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>97567661</v>
+      </c>
+      <c r="B4" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>201129</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycaena virgaureae</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ramsjö, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>535441</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6904748</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inventering för länsstyrelsen</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind, Tor Hansson Frank, Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>97567662</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>201129</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycaena virgaureae</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ramsjö, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>535437</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6904748</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Inventering för länsstyrelsen</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind, Tor Hansson Frank, Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>97567649</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43285</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>201143</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ängsblåvinge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cyaniris semiargus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ramsjö, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>535136</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6904679</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Inventering för länsstyrelsen</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind, Tor Hansson Frank, Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>97567651</v>
+      </c>
+      <c r="B7" t="n">
+        <v>43285</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>201143</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ängsblåvinge</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cyaniris semiargus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ramsjö, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>535144</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6904674</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Inventering för länsstyrelsen</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind, Tor Hansson Frank, Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55216-2022 artfynd.xlsx
+++ b/artfynd/A 55216-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119803564</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97567813</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97567661</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97567662</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97567649</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1291,8 +1321,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97567651</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>